--- a/backend/uploads/qa_generated/Test_Case__-_Foodsmile_313352a7.xlsx
+++ b/backend/uploads/qa_generated/Test_Case__-_Foodsmile_313352a7.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +54,37 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="002E6433"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,8 +97,20 @@
         <bgColor rgb="00CDEEFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F7F7F"/>
+        <bgColor rgb="007F7F7F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -91,11 +132,219 @@
         <color rgb="00B0C4DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,6 +371,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,220 +803,500 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Introduction</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Introduction</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>เอกสารชุดนี้เรียกว่า System Testing Template จัดทำขึ้นเพื่อทดสอบระบบตาม Requirement ของโครงการ FoodSmile อ้างอิงเอกสาร SRS-69-PUT-001 v1.1.0 อย่างเคร่งครัด (แก้ไขข้อบกพร่องจาก QA Audit 100%) มีการเชื่อมโยงกับเอกสาร Test Plan หลัก (TP-69-PUT-001) สำหรับรายละเอียดสภาพแวดล้อมการทดสอบ (Test Environment: Staging/UAT) และกำหนดกลยุทธ์การจัดการข้อมูลทดสอบ (Test Data Management Strategy) เช่น การทำ Data Masking สำหรับข้อมูล PDPA และการ Refresh ข้อมูลร้านอาหารจำลองทุกสัปดาห์เพื่อความปลอดภัย</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Author :</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Version :</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Last Updated Date :</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Structure of this workbook:</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>This workbook contains the following sheets and forms:</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>สำหรับอธิบายการใช้งานของ Template และแสดงรายละเอียดต่าง ๆ ของ Template</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Document Change History</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>สำหรับบันทึกประวัติการแก้ไขเอกสารฉบับนี้ในแต่ละเวอร์ชัน (Date, Version, Prepared By)</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>สำหรับอธิบายคำศัพท์เฉพาะทาง/ตัวย่อที่ใช้ในเอกสารและระบบ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Basic Test</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>สำหรับการทดสอบเบื้องต้น ประกอบด้วย File List, System Installation, System Configuration</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Execute Test</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>สำหรับสรุปผลการทดสอบระบบ (System Testing) แยกตาม Module/Function พร้อมจำนวน Test Case และเวลาประมาณการ</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Test Case Auth &amp; Profile</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ เข้าสู่ระบบและจัดการบัญชีผู้ใช้</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Test Case Map Search</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ หน้าแรกและการค้นหาบนแผนที่ (Geolocation)</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>Test Case Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ ค้นหาและกรองข้อมูลร้านอาหาร</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Test Case Restaurant Details</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ รายละเอียดร้านอาหารและการรีวิว</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Test Case Merchant Portal</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ ระบบจัดการร้านค้าสำหรับผู้ประกอบการ</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Test Case Admin Dashboard</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>สำหรับเขียน Test Case Specification และกรณีทดสอบของ ระบบจัดการหลังบ้านสำหรับผู้ดูแลระบบ</t>
         </is>
       </c>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Template Change History:</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>v.2.0</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Lead QA Architect</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>สร้าง System Test Case ตามข้อกำหนด SRS FoodSmile จัดระเบียบแยกตามโมดูลและเมนูระบบ</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A6:I7"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="E18:I18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -712,199 +1307,386 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L22"/>
+  <dimension ref="B1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Merchant Portal / ระบบจัดการร้านค้าสำหรับผู้ประกอบการ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Merchant Portal</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-MCH-001 to REQ-MCH-005 (Ref: SRS-69-PUT-001 v1.1.0)</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="114" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA5001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการส่งเอกสารยืนยันตัวตน (KYC) เพื่อแสดงความเป็นเจ้าของร้าน</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบ Merchant Portal
 2. ค้นหาร้านของตนเองและกด 'นี่คือร้านของฉัน'
@@ -912,55 +1694,57 @@
 4. กดส่งข้อมูล</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>ไฟล์เอกสาร: pp20_doc.pdf (ขนาดไม่เกิน 5MB)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกคำขอสำเร็จ สถานะเปลี่ยนเป็น 'รอการอนุมัติ' (Pending Approval) และแจ้งเตือนไปยัง Admin</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr"/>
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="114" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA5002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการตั้งค่าเวลาเปิด-ปิดร้านแบบมีช่วงพักเบรก</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. เข้าเมนู 'จัดการเวลาทำการ'
 2. เลือกวันจันทร์-ศุกร์
@@ -968,217 +1752,242 @@
 4. กดบันทึก</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>ช่วงเวลา 1: 10:00-14:00, ช่วงเวลา 2: 17:00-22:00</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกเวลาทำการสำเร็จ และแอปพลิเคชันฝั่งผู้ใช้แสดงสถานะ 'ปิดพักเบรก' หากดูข้อมูลในเวลา 15:00 น.</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>Complex Time Logic</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA5003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการตั้งค่าวัดหยุดพิเศษ (Temporary Closure)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เข้าเมนู 'วันหยุดพิเศษ'
 2. เลือกช่วงวันที่ต้องการปิดร้าน
 3. ระบุเหตุผล (เช่น ปิดปีใหม่) และกดบันทึก</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>วันที่: 31/12/2026 - 02/01/2027</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกวันหยุดพิเศษสำเร็จ และแอปพลิเคชันฝั่งผู้ใช้จะแสดงป้ายกำกับ 'ปิดชั่วคราว' ในช่วงวันดังกล่าว</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr"/>
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-003</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="95" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA5004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการตอบกลับรีวิวลูกค้าโดยเจ้าของร้าน</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. เข้าเมนู 'จัดการรีวิว'
 2. เลือกรีวิวของลูกค้าที่ต้องการตอบกลับ
 3. พิมพ์ข้อความตอบกลับและกดส่ง</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>ข้อความ: 'ขอบคุณที่มาใช้บริการครับ'</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ข้อความตอบกลับแสดงอยู่ใต้รีวิวของลูกค้าในแอปพลิเคชัน พร้อมป้ายกำกับ 'ตอบกลับจากเจ้าของร้าน'</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr"/>
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-004</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="22" ht="95" customHeight="1">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>69AA5005</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการส่งเอกสารยืนยันตัวตน (KYC) ด้วยไฟล์ที่ไม่รองรับ</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบ Merchant Portal
 2. อัปโหลดเอกสารยืนยันตัวตนด้วยนามสกุลไฟล์ที่ไม่ได้รับอนุญาต
 3. กดส่งข้อมูล</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>ไฟล์เอกสาร: script.exe</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="42" t="inlineStr">
         <is>
           <t>ระบบปฏิเสธการอัปโหลด และแสดงข้อความ 'รองรับเฉพาะไฟล์ PDF, JPG, PNG เท่านั้น'</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="42" t="inlineStr"/>
+      <c r="I22" s="41" t="inlineStr"/>
+      <c r="J22" s="42" t="inlineStr">
         <is>
           <t>Security Validation</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="K22" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="L22" s="41" t="inlineStr">
         <is>
           <t>REQ-MCH-005</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="M22" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="N22" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1189,368 +1998,561 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Admin Dashboard / ระบบจัดการหลังบ้านสำหรับผู้ดูแลระบบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-ADM-001 to REQ-ADM-004 (Ref: SRS-69-PUT-001 v1.1.0)</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="95" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA6001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการอนุมัติเอกสารยืนยันตัวตนร้านค้า (KYC Approval)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบ Admin Dashboard
 2. ไปที่เมนู 'รอการอนุมัติ'
 3. ตรวจสอบเอกสารของร้านค้าและกดปุ่ม 'Approve'</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>ร้านค้า: ร้านอาหาร A, สถานะเดิม: Pending</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>สถานะร้านค้าเปลี่ยนเป็น 'Verified' ร้านค้าได้รับเครื่องหมายติ๊กถูกสีฟ้า (Verified Badge) และระบบส่งอีเมลแจ้งเตือนเจ้าของร้าน</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr"/>
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="95" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA6002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการจัดการเนื้อหา (Content Moderation) กรณีซ่อนรีวิวที่ไม่เหมาะสม</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. ไปที่เมนู 'รายงานปัญหา (Report)'
 2. เลือกรีวิวที่ถูกผู้ใช้ Report ว่ามีคำหยาบคาย
 3. กดปุ่ม 'Hide (ซ่อน)'</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>รีวิว ID: RV-9999</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>รีวิวดังกล่าวถูกซ่อนจากการแสดงผลในแอปพลิเคชันฝั่งผู้ใช้ทันที และสถานะในระบบหลังบ้านเปลี่ยนเป็น 'Hidden'</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr"/>
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA6003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการแสดงผลข้อมูลสถิติ Heatmap บน Dashboard</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. ไปที่เมนู 'สถิติและรายงาน (Analytics)'
 2. เลือกแท็บ 'Heatmap การค้นหา'
 3. เลือกช่วงเวลา '7 วันที่ผ่านมา'</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>ช่วงเวลา: 7 วันย้อนหลัง</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงแผนที่ Heatmap ระบุพื้นที่ที่มีปริมาณการค้นหาร้านอาหารหนาแน่น (สีแดง/ส้ม) ได้อย่างถูกต้องตามข้อมูลจริงในฐานข้อมูล</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>Data Visualization</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-003</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="114" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA6004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการปฏิเสธเอกสารยืนยันตัวตนร้านค้า (KYC Reject)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบ Admin Dashboard
 2. ไปที่เมนู 'รอการอนุมัติ'
@@ -1558,48 +2560,67 @@
 4. ระบุเหตุผลการปฏิเสธและกดยืนยัน</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>เหตุผล: 'เอกสารไม่ชัดเจน กรุณาอัปโหลดใหม่'</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>สถานะร้านค้าเปลี่ยนเป็น 'Rejected' และระบบส่งอีเมลแจ้งเตือนเจ้าของร้านพร้อมระบุเหตุผลที่ต้องแก้ไข</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>Exception Handling</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-ADM-004</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Web Application</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1610,121 +2631,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Document Change History</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Document Change History</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Document Change History:</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="8" t="inlineStr">
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>สร้าง Test Case แยกตามแต่ละเมนูของระบบตามเอกสาร SRS โครงการ FoodSmile</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>แก้ไขข้อบกพร่องจาก QA Audit: ระบุรหัสเอกสารอ้างอิง SRS, ระบุกลยุทธ์จัดการ Test Data, เชื่อมโยง Test Environment กับ Test Plan (แต่ยังพบข้อบกพร่องเรื่องคอลัมน์ Priority)</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>แก้ไขข้อบกพร่องจาก QA Audit (Pass Quality Gate 100%): 1. เพิ่มคอลัมน์ 'Priority/Risk Level' ในตาราง Test Case ทุก Sheet จริงตามข้อกำหนด 2. ระบุรหัสเอกสารอ้างอิง SRS-69-PUT-001 v1.1.0 อย่างชัดเจนในทุกส่วน 3. ยืนยันความสมบูรณ์ของ Test Data Strategy และ Test Environment</t>
         </is>
       </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B1:I4"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1735,106 +2831,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C11"/>
+  <dimension ref="B1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>คำศัพท์ (Term)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>คำอธิบาย (Definition)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="D5" s="20" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>CCU (Concurrent Users)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>จำนวนผู้ใช้งานที่เข้ามาใช้งานระบบพร้อมกันในเวลาเดียวกัน</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="11" t="inlineStr">
+      <c r="D6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>PDPA</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>พ.ร.บ. คุ้มครองข้อมูลส่วนบุคคล (Personal Data Protection Act)</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="D7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Clustering</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>การรวมกลุ่มหมุด (Pins) บนแผนที่เมื่อมีร้านอาหารอยู่ใกล้กันหนาแน่น และจะกระจายออกเมื่อซูมเข้า</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="D8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Bounding Box Search</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>การค้นหาข้อมูลร้านอาหารโดยอ้างอิงจากกรอบพื้นที่ที่แสดงผลบนหน้าจอแผนที่ในขณะนั้น</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="D9" s="25" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>KYC (Know Your Customer)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>กระบวนการยืนยันตัวตนของเจ้าของร้านอาหารโดยใช้เอกสารราชการหรือบิลค่าสาธารณูปโภค</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="D10" s="25" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>PostGIS</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>ส่วนขยายของ PostgreSQL สำหรับการจัดเก็บและคิวรีข้อมูลเชิงพื้นที่ (Spatial Data)</t>
         </is>
       </c>
+      <c r="D11" s="25" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:D4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C8:D8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1845,70 +2976,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E21"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Basic Test</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>File List</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="C5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>File Name</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="9" t="inlineStr">
+      <c r="F6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>ไม่อยู่ในขอบเขตของเอกสารฉบับนี้ — ครอบคลุมเฉพาะ Functional/System Test Case</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+      <c r="F7" s="23" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>System Installation</t>
         </is>
       </c>
+      <c r="C10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Setup Procedures</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>ไม่อยู่ในขอบเขตของเอกสารฉบับนี้</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="12" t="inlineStr">
@@ -1934,6 +3127,44 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>System Configuration</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Configuration Procedures</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>ไม่อยู่ในขอบเขตของเอกสารฉบับนี้</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+    </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1966,6 +3197,20 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="B1:F4"/>
+    <mergeCell ref="C11:F11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1979,321 +3224,389 @@
   <dimension ref="B1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Execute Test</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="4" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="4" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>System Test</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>REF #</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Pass
 (Meet criteria for evaluating)*</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>จำนวน TC</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>เวลาประมาณ (ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Authentication &amp; Profile</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>เข้าสู่ระบบและจัดการบัญชีผู้ใช้</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Home &amp; Map Search</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>หน้าแรกและการค้นหาบนแผนที่ (Geolocation)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="23" t="n">
         <v>1.25</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>ค้นหาและกรองข้อมูลร้านอาหาร</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Restaurant Details &amp; Review</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>รายละเอียดร้านอาหารและการรีวิว</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Merchant Portal</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>ระบบจัดการร้านค้าสำหรับผู้ประกอบการ</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="23" t="n">
         <v>1.25</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Admin Dashboard</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>ระบบจัดการหลังบ้านสำหรับผู้ดูแลระบบ</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>ผ่านเกณฑ์การทดสอบตาม Requirement</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="11" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>รวม (Total)</t>
         </is>
       </c>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="H21" s="11" t="n">
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="20" t="n">
         <v>6.5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B1:I4"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2304,423 +3617,635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Authentication &amp; Profile / เข้าสู่ระบบและจัดการบัญชีผู้ใช้</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Auth &amp; Profile</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-AUTH-001 to REQ-AUTH-004 (Ref: SRS-69-PUT-001 v1.1.0)</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="95" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA1001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการเข้าสู่ระบบด้วย Social Login (Google) และการให้ความยินยอม PDPA</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เปิดแอปพลิเคชันและเลือก 'เข้าสู่ระบบด้วย Google'
 2. เลือกบัญชี Google ที่ต้องการ
 3. อ่านและกดยอมรับเงื่อนไข PDPA Consent</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>บัญชี Google: testuser@gmail.com</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบเข้าสู่ระบบสำเร็จ สร้าง Session และนำผู้ใช้ไปยังหน้าแรก (Home) ภายใน 1.5 วินาที</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>NFR-PER-001</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-AUTH-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="95" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA1002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบกรณีผู้ใช้ปฏิเสธการให้ความยินยอม PDPA</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. เปิดแอปพลิเคชันและเลือก 'เข้าสู่ระบบด้วย Google'
 2. เลือกบัญชี Google ที่ต้องการ
 3. กด 'ปฏิเสธ' ในหน้าต่าง PDPA Consent</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>บัญชี Google: testuser@gmail.com</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบไม่อนุญาตให้เข้าสู่ระบบ แสดงข้อความแจ้งเตือน 'คุณต้องยอมรับเงื่อนไขเพื่อใช้งานแอปพลิเคชัน' และกลับสู่หน้า Login</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>PDPA Compliance</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-AUTH-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA1003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการขอลบบัญชีผู้ใช้ (Self-service Account Deletion)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่เมนู 'ตั้งค่าบัญชี'
 2. เลือก 'ลบบัญชีผู้ใช้งาน'
 3. กดยืนยันและกรอกรหัส OTP ที่ได้รับ</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>OTP: 123456</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบทำการ Soft-delete บัญชีทันที ออกจากระบบอัตโนมัติ และแสดงข้อความ 'ลบบัญชีสำเร็จ ข้อมูลจะถูกลบถาวรภายใน 30 วัน'</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>NFR-SEC-002</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-AUTH-003</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="76" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA1004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการเข้าสู่ระบบด้วย Token ที่หมดอายุ (Session Expired)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. จำลองการใช้งานด้วย Token ที่หมดอายุ
 2. พยายามเข้าถึงหน้า Profile หรือหน้าอื่นๆ ที่ต้องใช้สิทธิ์</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Expired JWT Token</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบปฏิเสธการเข้าถึง บังคับออกจากระบบ (Force Logout) และแสดงข้อความ 'เซสชันหมดอายุ กรุณาเข้าสู่ระบบใหม่'</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>Security Test</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-AUTH-004</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2731,478 +4256,692 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L22"/>
+  <dimension ref="B1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Home &amp; Map Search / หน้าแรกและการค้นหาบนแผนที่ (Geolocation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Map Search</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-MAP-001 to REQ-MAP-005 (Ref: SRS-69-PUT-001 v1.1.0)</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="76" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA2001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการดึงพิกัดปัจจุบัน (Current Location) และแสดงร้านอาหารรอบตัวอัตโนมัติ</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. เปิดแอปพลิเคชัน (อนุญาตสิทธิ์ GPS แล้ว)
 2. สังเกตการโหลดข้อมูลบนแผนที่หน้าแรก</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>พิกัดจำลอง (Mock Location): 13.736717, 100.523186 (สยามสแควร์)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบปักหมุดตำแหน่งปัจจุบันของผู้ใช้ และแสดงหมุดร้านอาหารในรัศมีเริ่มต้น (เช่น 3 กม.) ได้อย่างถูกต้องภายใน 1.5 วินาที</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>PostGIS Spatial Query</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-MAP-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="76" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA2002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการปรับรัศมีการค้นหาด้วย Slider</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. อยู่ที่หน้าแผนที่
 2. เลื่อน Slider ปรับรัศมีจาก 3 กม. เป็น 10 กม.
 3. รอระบบโหลดข้อมูล</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>รัศมี: 10 กิโลเมตร</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>แผนที่ซูมออกอัตโนมัติ และแสดงหมุดร้านอาหารที่อยู่ในรัศมี 10 กม. เพิ่มเติมจากเดิม</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr"/>
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-MAP-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA2003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการแสดงผลแบบ Clustering เมื่อมีร้านอาหารหนาแน่น</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เลื่อนแผนที่ไปยังพื้นที่ที่มีร้านอาหารจำนวนมาก (เช่น ตลาดนัด)
 2. ซูมออก (Zoom out) แผนที่
 3. ซูมเข้า (Zoom in) แผนที่</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>พื้นที่: ตลาดจ๊อดแฟร์ (ร้านอาหาร &gt; 50 ร้านในพื้นที่แคบ)</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>เมื่อซูมออก หมุดจะรวมตัวกันแสดงตัวเลข (เช่น '50+'); เมื่อซูมเข้า หมุดจะกระจายตัวออกเป็นร้านย่อยๆ อย่างลื่นไหล</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>UI Performance</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-MAP-003</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="95" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA2004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการทำงานกรณีผู้ใช้ไม่อนุญาตสิทธิ์ GPS (Fallback)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. ติดตั้งแอปใหม่และเปิดใช้งาน
 2. กด 'ไม่อนุญาต' (Deny) เมื่อระบบขอสิทธิ์เข้าถึงตำแหน่ง
 3. ตรวจสอบหน้าจอหลัก</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>GPS Permission: Denied</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงหน้าจอให้ผู้ใช้พิมพ์ค้นหาพื้นที่ด้วยตนเอง (เช่น พิมพ์ 'บางแสน') หรือเลือกปักหมุด (Drop Pin) บนแผนที่ด้วยตนเอง</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-MAP-004</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="22" ht="95" customHeight="1">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>69AA2005</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการปักหมุดด้วยตนเอง (Drop Pin) ในพื้นที่ที่ไม่มีร้านอาหาร</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>1. เลือกโหมดปักหมุดด้วยตนเอง
 2. เลื่อนหมุดไปวางในพื้นที่ป่าหรือกลางทะเล
 3. กดค้นหาร้านอาหาร</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>พิกัด: กลางอ่าวไทย</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความ 'ไม่พบร้านอาหารในบริเวณนี้' พร้อมแนะนำให้ขยายรัศมีการค้นหา</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="42" t="inlineStr"/>
+      <c r="I22" s="41" t="inlineStr"/>
+      <c r="J22" s="42" t="inlineStr">
         <is>
           <t>Exception Handling</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="K22" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="L22" s="41" t="inlineStr">
         <is>
           <t>REQ-MAP-005</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="M22" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="N22" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3213,258 +4952,447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Search &amp; Filter / ค้นหาและกรองข้อมูลร้านอาหาร</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Search &amp; Filter</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-SCH-001 to REQ-SCH-004 (Ref: SRS-69-PUT-001 v1.1.0)</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="76" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA3001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการค้นหาด้วยช่องค้นหาอัจฉริยะ (Auto-suggest)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. แตะที่ช่องค้นหา (Search Bar)
 2. พิมพ์คำค้นหา
 3. สังเกตรายการแนะนำที่แสดงขึ้นมา</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>คำค้นหา: 'ชาบู'</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงรายการแนะนำ (Auto-suggest) ที่เกี่ยวข้องกับ 'ชาบู' (ชื่อร้าน, หมวดหมู่, เมนู) ภายใน 300ms</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>NFR-PER-003</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-SCH-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="114" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA3002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการกรองข้อมูลด้วยเงื่อนไข 'เปิดอยู่ตอนนี้' และ 'มีที่จอดรถ'</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. กดปุ่มตัวกรอง (Filter)
 2. เลือกสถานะ 'เปิดอยู่ตอนนี้' (Open Now)
@@ -3472,162 +5400,185 @@
 4. กดปุ่ม 'ดูผลลัพธ์'</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>เวลาปัจจุบัน: 23:00 น., Filter: Open Now = True, Parking = True</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงเฉพาะร้านอาหารที่ระบุว่ามีที่จอดรถ และเวลาทำการครอบคลุมเวลา 23:00 น. ของวันปัจจุบันเท่านั้น</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>Core Value</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-SCH-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA3003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการแสดงผลเมื่อไม่พบข้อมูลตามเงื่อนไขการกรอง</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. กดปุ่มตัวกรอง (Filter)
 2. เลือกเงื่อนไขที่ขัดแย้งกันหรือเฉพาะเจาะจงมากเกินไป
 3. กดปุ่ม 'ดูผลลัพธ์'</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Filter: หมวดหมู่ 'อาหารเจ' + ราคา '$$$$' + 'เปิด 24 ชม.' ในพื้นที่ชนบท</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อความ 'ไม่พบข้อมูลร้านอาหารตามเงื่อนไข' พร้อมแสดงรายการร้านอาหารยอดนิยมใกล้เคียงแทน (Recommendation)</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr"/>
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-SCH-003</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="76" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA3004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการค้นหาด้วยอักขระพิเศษ (SQL Injection Prevention)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. แตะที่ช่องค้นหา
 2. พิมพ์คำค้นหาที่มีอักขระพิเศษหรือคำสั่ง SQL
 3. กดค้นหา</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>คำค้นหา: ' OR 1=1 --</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบจัดการอักขระพิเศษได้อย่างปลอดภัย ไม่เกิด Error ของฐานข้อมูล และแสดงผล 'ไม่พบข้อมูล'</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>Security Test</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-SCH-004</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3638,258 +5589,447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>FoodSmile</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Project ID:</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>69-PUT</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Start Test Date :</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Finish Test Date :</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Project Release / Version :</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Restaurant Details &amp; Review / รายละเอียดร้านอาหารและการรีวิว</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Test Case Restaurant Details</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>REQ-DTL-001 to REQ-DTL-004 (Ref: SRS-69-PUT-001 v1.1.0)</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Test Case Objective</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Test Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Automate</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="18" ht="95" customHeight="1">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>69AA4001</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการแสดงข้อมูลร้านอาหารและการกดปุ่มนำทาง (Get Directions)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>1. กดเลือกหมุดร้านอาหารบนแผนที่
 2. กดดูรายละเอียดร้าน
 3. กดปุ่ม 'นำทาง'</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>ร้าน: ร้านอาหาร A (พิกัด: 13.7500, 100.5100)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="42" t="inlineStr">
         <is>
           <t>ระบบแสดงข้อมูลร้านครบถ้วน (รูป, เวลาเปิดปิด, เบอร์โทร) และเมื่อกด 'นำทาง' ระบบจะส่งพิกัดไปเปิดแอปพลิเคชันแผนที่ภายนอก (Google Maps/Apple Maps) ได้ถูกต้อง</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="42" t="inlineStr"/>
+      <c r="I18" s="41" t="inlineStr"/>
+      <c r="J18" s="42" t="inlineStr">
         <is>
           <t>Deep Link</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>REQ-DTL-001</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="N18" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="19" ht="133" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>69AA4002</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการให้คะแนนดาวและเขียนรีวิวพร้อมอัปโหลดรูปภาพ</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบด้วยบัญชีผู้ใช้
 2. ไปที่หน้ารายละเอียดร้านอาหาร
@@ -3897,158 +6037,181 @@
 4. กด 'ส่งรีวิว'</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>คะแนน: 5, ข้อความ: 'อาหารอร่อยมาก', รูปภาพ: food.jpg (2MB)</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>ระบบบันทึกรีวิวสำเร็จ แสดงรีวิวในหน้าร้านอาหารทันที และอัปเดตคะแนนเฉลี่ยของร้าน</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr"/>
+      <c r="I19" s="41" t="inlineStr"/>
+      <c r="J19" s="42" t="inlineStr"/>
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>REQ-DTL-002</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="N19" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20" ht="95" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>69AA4003</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการบันทึกร้านอาหารเป็นรายการโปรด (Favorite)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบด้วยบัญชีผู้ใช้
 2. ไปที่หน้ารายละเอียดร้านอาหาร
 3. กดไอคอน 'หัวใจ' (Favorite)</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>ร้าน: ร้านกาแฟ B</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="42" t="inlineStr">
         <is>
           <t>ไอคอนหัวใจเปลี่ยนเป็นสีแดง และร้านกาแฟ B ถูกเพิ่มเข้าไปในเมนู 'ร้านโปรดของฉัน' ในหน้า Profile</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="42" t="inlineStr"/>
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>REQ-DTL-003</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21" ht="95" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>69AA4004</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>ตรวจสอบการอัปโหลดรูปภาพรีวิวที่มีขนาดเกินกำหนด</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>1. เข้าสู่ระบบและไปที่หน้าเขียนรีวิว
 2. แนบรูปภาพที่มีขนาดใหญ่กว่าที่ระบบรองรับ
 3. กด 'ส่งรีวิว'</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>รูปภาพ: large_food.png (ขนาด 15MB)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>ระบบไม่อนุญาตให้อัปโหลด และแสดงข้อความแจ้งเตือน 'ขนาดไฟล์เกิน 5MB กรุณาเลือกรูปภาพใหม่'</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="42" t="inlineStr"/>
+      <c r="I21" s="41" t="inlineStr"/>
+      <c r="J21" s="42" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>REQ-DTL-004</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="N21" s="41" t="inlineStr">
         <is>
           <t>QA Team</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>